--- a/human_resources_forms/005_staff_holiday_gift_selection--human_resources_forms.xlsx
+++ b/human_resources_forms/005_staff_holiday_gift_selection--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'in-person_delivery'}</t>
+          <t>in-person_delivery</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'In-person delivery'}</t>
+          <t>In-person delivery</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'mail_delivery'}</t>
+          <t>mail_delivery</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Mail delivery'}</t>
+          <t>Mail delivery</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both_options'}</t>
+          <t>both_options</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Both options'}</t>
+          <t>Both options</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'no_delivery'}</t>
+          <t>no_delivery</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'No delivery'}</t>
+          <t>No delivery</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'gift_card'}</t>
+          <t>gift_card</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Gift Card'}</t>
+          <t>Gift Card</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'physical_gift'}</t>
+          <t>physical_gift</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Physical Gift'}</t>
+          <t>Physical Gift</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both_options'}</t>
+          <t>both_options</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Both options'}</t>
+          <t>Both options</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'no_gift'}</t>
+          <t>no_gift</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'No gift'}</t>
+          <t>No gift</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'i_confirm_i_will_receive_my_gift'}</t>
+          <t>i_confirm_i_will_receive_my_gift</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'I confirm I will receive my gift'}</t>
+          <t>I confirm I will receive my gift</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_yet'}</t>
+          <t>not_yet</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Not yet'}</t>
+          <t>Not yet</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unable_to_confirm'}</t>
+          <t>unable_to_confirm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Unable to confirm'}</t>
+          <t>Unable to confirm</t>
         </is>
       </c>
     </row>
